--- a/2026/MLMLG_2026/Excel/TC_BS_USD.xlsx
+++ b/2026/MLMLG_2026/Excel/TC_BS_USD.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\GitHub\UMSA\2026\MLMLG_2026\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ED88E054-2110-4733-8191-E0B525F56443}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACC71D5A-72E6-45A5-84C2-134D447E9D73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="0" windowWidth="26100" windowHeight="15585" xr2:uid="{938F6879-023C-4E4E-9600-82FE8D0BE802}"/>
+    <workbookView xWindow="4455" yWindow="3360" windowWidth="23790" windowHeight="11295" activeTab="1" xr2:uid="{938F6879-023C-4E4E-9600-82FE8D0BE802}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1 (2)" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,6 +37,20 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+  <si>
+    <t>alpha</t>
+  </si>
+  <si>
+    <t>beta</t>
+  </si>
+  <si>
+    <t>beta2</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -69,8 +84,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -89,6 +105,1663 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1440" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Tipo de Cambio Bs./USD</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.7270778652668435E-2"/>
+          <c:y val="4.1666666666666664E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1440" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$A$1:$A$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$B$1:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>9.73</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.76</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.76</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.7799999999999994</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.83</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.83</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.83</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.89</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.9600000000000009</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10.1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10.24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1F6E-4467-8F32-68B9302434A1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1287636591"/>
+        <c:axId val="857107279"/>
+      </c:barChart>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$A$1:$A$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$C$1:$C$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1F6E-4467-8F32-68B9302434A1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1287639375"/>
+        <c:axId val="857090479"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1287636591"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>fecha: Junio/Julio</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="857107279"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="857107279"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>bs./Usd</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1287636591"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="857090479"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1287639375"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="1287639375"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="857090479"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1200"/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1440" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Tipo de Cambio Bs./USD</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.7270778652668435E-2"/>
+          <c:y val="4.1666666666666664E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1440" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="69850" cap="rnd" cmpd="sng">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="poly"/>
+            <c:order val="3"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$A$1:$A$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$B$1:$B$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>9.73</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.76</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.76</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.7799999999999994</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.83</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.83</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.83</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.89</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.9600000000000009</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10.1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10.24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-3B49-4D36-8A4C-CE492EC8C77B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="69"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1287636591"/>
+        <c:axId val="857107279"/>
+      </c:barChart>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$A$1:$A$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$C$1:$C$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-3B49-4D36-8A4C-CE492EC8C77B}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1287639375"/>
+        <c:axId val="857090479"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1287636591"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>fecha: Junio/Julio</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="857107279"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="857107279"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>bs./Usd</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1287636591"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="857090479"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1287639375"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="1287639375"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="857090479"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr sz="1200"/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>'Sheet1 (2)'!$B$1:$B$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="23"/>
+                <c:pt idx="0">
+                  <c:v>9.73</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.76</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.76</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.7799999999999994</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.83</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.83</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.83</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.89</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.9600000000000009</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10.1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10.24</c:v>
+                </c:pt>
+                <c:pt idx="12" formatCode="0.00">
+                  <c:v>10.180999999999999</c:v>
+                </c:pt>
+                <c:pt idx="13" formatCode="0.00">
+                  <c:v>10.3545</c:v>
+                </c:pt>
+                <c:pt idx="14" formatCode="0.00">
+                  <c:v>10.43675</c:v>
+                </c:pt>
+                <c:pt idx="15" formatCode="0.00">
+                  <c:v>10.591624999999999</c:v>
+                </c:pt>
+                <c:pt idx="16" formatCode="0.00">
+                  <c:v>10.739187499999998</c:v>
+                </c:pt>
+                <c:pt idx="17" formatCode="0.00">
+                  <c:v>10.921406249999999</c:v>
+                </c:pt>
+                <c:pt idx="18" formatCode="0.00">
+                  <c:v>11.119296874999998</c:v>
+                </c:pt>
+                <c:pt idx="19" formatCode="0.00">
+                  <c:v>11.344351562499998</c:v>
+                </c:pt>
+                <c:pt idx="20" formatCode="0.00">
+                  <c:v>11.59282421875</c:v>
+                </c:pt>
+                <c:pt idx="21" formatCode="0.00">
+                  <c:v>11.868587890624999</c:v>
+                </c:pt>
+                <c:pt idx="22" formatCode="0.00">
+                  <c:v>12.171706054687499</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B067-4B73-BC57-026C3B82F5CC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1439072687"/>
+        <c:axId val="788107727"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1439072687"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="788107727"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="788107727"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="9"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1439072687"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -698,6 +2371,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="857090479"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -755,7 +2429,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1423,6 +3097,294 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$1:$B$23</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="23"/>
+                <c:pt idx="0">
+                  <c:v>9.73</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9.76</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>9.76</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9.7799999999999994</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.8000000000000007</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.83</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.83</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>9.83</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.89</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.9600000000000009</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10.1</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>10.24</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E22E-40B9-B937-B7E847E7208F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1439072687"/>
+        <c:axId val="788107727"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1439072687"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="788107727"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="788107727"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:min val="9"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1439072687"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1503,6 +3465,166 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -2509,7 +4631,2164 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>161923</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>90487</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>104774</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09920256-8D0E-4E78-A279-20BDBA889030}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>119063</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DA1D4DF8-A0C1-4A63-9775-BABE9F5C9C3A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>42862</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C7C1EB1-F433-4B39-B4E0-56EF00909A48}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -2580,6 +6859,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDA80659-5B1C-1484-6F26-0CAE0C575ACE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2904,8 +7219,232 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93FE3E00-44E4-41BC-A430-D262CB9EEB16}">
+  <dimension ref="A1:E23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>29</v>
+      </c>
+      <c r="B1">
+        <v>9.73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>30</v>
+      </c>
+      <c r="B2">
+        <v>9.76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>9.76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>9.7799999999999994</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>9.8000000000000007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>9.83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <v>9.83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <v>9.83</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <v>9.89</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <v>9.9600000000000009</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>10.1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>10.24</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1">
+        <f>+$E$11*B12+(1-$E$11)*B11+$E$12*A13 + $E$13*A13^2</f>
+        <v>10.180999999999999</v>
+      </c>
+      <c r="D13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1">
+        <f t="shared" ref="B14:B23" si="0">+$E$11*B13+(1-$E$11)*B12+$E$12*A14^2</f>
+        <v>10.3545</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1">
+        <f t="shared" si="0"/>
+        <v>10.43675</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1">
+        <f t="shared" si="0"/>
+        <v>10.591624999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1">
+        <f t="shared" si="0"/>
+        <v>10.739187499999998</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1">
+        <f t="shared" si="0"/>
+        <v>10.921406249999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1">
+        <f t="shared" si="0"/>
+        <v>11.119296874999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1">
+        <f t="shared" si="0"/>
+        <v>11.344351562499998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1">
+        <f t="shared" si="0"/>
+        <v>11.59282421875</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1">
+        <f t="shared" si="0"/>
+        <v>11.868587890624999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" s="1">
+        <f t="shared" si="0"/>
+        <v>12.171706054687499</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D50626DC-9AAF-4056-9EB3-38A44143CD99}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -3003,6 +7542,72 @@
       <c r="B12">
         <v>10.24</v>
       </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1"/>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1"/>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1"/>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1"/>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1"/>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>21</v>
+      </c>
+      <c r="B23" s="1"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:B12">
